--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104599_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104599_W16.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2919</v>
+        <v>4.3513</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2814</v>
+        <v>2.5319</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0104</v>
+        <v>1.8194</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0588</v>
+        <v>2.0504</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5918</v>
+        <v>2.5743</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.533</v>
+        <v>-0.5239</v>
       </c>
       <c r="J2" t="n">
-        <v>1.5355</v>
+        <v>1.5009</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2472</v>
+        <v>2.2161</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5233</v>
+        <v>0.5495</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9136</v>
+        <v>0.9838</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0143</v>
+        <v>1.3073</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1007</v>
+        <v>-0.3235</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4826</v>
+        <v>3.1509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4431</v>
+        <v>0.9041</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0395</v>
+        <v>2.2468</v>
       </c>
       <c r="G3" t="n">
-        <v>1.253</v>
+        <v>1.2649</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9811</v>
+        <v>0.9876</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2719</v>
+        <v>0.2773</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.123</v>
+        <v>-0.1291</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5888</v>
+        <v>0.5861</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>1.376</v>
+        <v>1.3941</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1615</v>
+        <v>0.8177</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4053</v>
+        <v>0.8754</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2438</v>
+        <v>-0.0578</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1107</v>
+        <v>2.9363</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9755</v>
+        <v>1.4006</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1352</v>
+        <v>1.5357</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0732</v>
+        <v>-0.0717</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8887</v>
+        <v>1.8979</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.9619</v>
+        <v>-1.9696</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4711</v>
+        <v>-0.4921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.3542</v>
+        <v>-1.3712</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3979</v>
+        <v>0.4204</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0055</v>
+        <v>1.0189</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4966</v>
+        <v>0.3251</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3539</v>
+        <v>0.8033</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8505</v>
+        <v>-0.4782</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. BIRGANDER</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5608</v>
+        <v>1.5679</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0345</v>
+        <v>-0.6382</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5953</v>
+        <v>2.2061</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4034</v>
+        <v>1.2612</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3795</v>
+        <v>0.8618</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0239</v>
+        <v>0.3993</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2659</v>
+        <v>1.2693</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3779</v>
+        <v>0.7337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.112</v>
+        <v>0.5355</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1375</v>
+        <v>-0.0081</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0017</v>
+        <v>0.1281</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1359</v>
+        <v>-0.1362</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-3.6421</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0569</v>
+        <v>-0.03</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7512</v>
+        <v>0.4874</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3058</v>
+        <v>-0.5174</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>1.2472</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3856</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ALLEN</t>
+          <t>S. BIRGANDER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2268</v>
+        <v>0.4399</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2268</v>
+        <v>1.5979</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0.3893</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.3764</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.0129</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.2782</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.3899</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.1111</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.1246</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.9187</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.6454</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.2733</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>M. ALLEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0866</v>
+        <v>0.2276</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.638</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7245</v>
+        <v>0.2276</v>
       </c>
       <c r="G7" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8658</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3972</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3096</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7579</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5516</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0466</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1079</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1545</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5225</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5716</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9509</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7088</v>
+        <v>-0.7511</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1695</v>
+        <v>-0.0738</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5394</v>
+        <v>-0.6773</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4159</v>
+        <v>-0.4144</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9595</v>
+        <v>0.962</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3754</v>
+        <v>-1.3765</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3853</v>
+        <v>1.3789</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2285</v>
+        <v>-0.2141</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6125</v>
+        <v>-0.6538</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1255</v>
+        <v>-0.2843</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W8" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3699</v>
+        <v>-1.5209</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3955</v>
+        <v>-2.5551</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0256</v>
+        <v>1.0342</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0917</v>
+        <v>-1.0959</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3824</v>
+        <v>0.382</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4741</v>
+        <v>-1.4779</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.7876</v>
+        <v>-1.8001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5727</v>
+        <v>-1.5793</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6959</v>
+        <v>0.7043</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6028</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6291</v>
+        <v>0.4855</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5263</v>
+        <v>0.3831</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1028</v>
+        <v>0.1024</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8908</v>
+        <v>-2.744</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4401</v>
+        <v>-5.0469</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5493</v>
+        <v>2.3029</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3026</v>
+        <v>-2.2913</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1976</v>
+        <v>0.2036</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5002</v>
+        <v>-2.4949</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0637</v>
+        <v>-2.0816</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1834</v>
+        <v>0.1756</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2389</v>
+        <v>-0.2097</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2265</v>
+        <v>0.3684</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2934</v>
+        <v>0.1321</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5199</v>
+        <v>0.2363</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. RUBIO</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0148</v>
+        <v>-2.8487</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.306</v>
+        <v>-0.3545</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2912</v>
+        <v>-2.4941</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4935</v>
+        <v>-2.1518</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2726</v>
+        <v>-0.15</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2209</v>
+        <v>-2.0018</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1182</v>
+        <v>0.612</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3432</v>
+        <v>0.9997</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.775</v>
+        <v>-0.3877</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6247</v>
+        <v>-2.7638</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9294</v>
+        <v>-1.1497</v>
       </c>
       <c r="O11" t="n">
-        <v>1.5541</v>
+        <v>-1.6141</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8562</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8976</v>
+        <v>-1.3658</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4425</v>
+        <v>-0.2903</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1785</v>
+        <v>0.3992</v>
       </c>
       <c r="U11" t="n">
-        <v>0.264</v>
+        <v>-0.6895</v>
       </c>
       <c r="V11" t="n">
-        <v>2.8924</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>4.5314</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.639</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>R. RUBIO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6681</v>
+        <v>-3.0215</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.325</v>
+        <v>-4.2528</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3431</v>
+        <v>1.2313</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1689</v>
+        <v>-2.5013</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1618</v>
+        <v>-1.2751</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0071</v>
+        <v>-1.2262</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6258</v>
+        <v>-3.1493</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0044</v>
+        <v>-0.3555</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3786</v>
+        <v>-2.7939</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7947</v>
+        <v>0.6481</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1662</v>
+        <v>-0.9196</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6285</v>
+        <v>1.5677</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-5.9184</v>
       </c>
       <c r="R12" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.087</v>
+        <v>0.4681</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5898</v>
+        <v>0.2993</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4972</v>
+        <v>0.1688</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>2.8814</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.5157</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9613</v>
+        <v>-3.5515</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8771</v>
+        <v>-3.4519</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0842</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4503</v>
+        <v>-0.4426</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3174</v>
+        <v>0.3215</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.764</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1514</v>
+        <v>0.1439</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6017</v>
+        <v>-0.5865</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0159</v>
+        <v>-0.605</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6261</v>
+        <v>-0.1813</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3899</v>
+        <v>-0.4237</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.854300000000001</v>
+        <v>-1.7638</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.4857</v>
+        <v>-12.6946</v>
       </c>
       <c r="F14" t="n">
-        <v>10.6311</v>
+        <v>10.9309</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.8247</v>
+        <v>-4.7818</v>
       </c>
       <c r="H14" t="n">
-        <v>6.370400000000001</v>
+        <v>6.3892</v>
       </c>
       <c r="I14" t="n">
-        <v>-11.195</v>
+        <v>-11.1711</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.3946</v>
+        <v>-4.6046</v>
       </c>
       <c r="K14" t="n">
-        <v>7.014699999999999</v>
+        <v>6.8993</v>
       </c>
       <c r="L14" t="n">
-        <v>-11.4091</v>
+        <v>-11.5042</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4301000000000007</v>
+        <v>-0.1768999999999993</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6443999999999999</v>
+        <v>-0.5098999999999998</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2141000000000001</v>
+        <v>0.333</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.6709</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.6833</v>
+        <v>-22.7633</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0122</v>
+        <v>17.0722</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6956000000000002</v>
+        <v>2.7882</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6617</v>
+        <v>4.7817</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.966</v>
+        <v>-1.9936</v>
       </c>
       <c r="V14" t="n">
-        <v>5.9455</v>
+        <v>5.920599999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>9.9306</v>
+        <v>9.8916</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.9851</v>
+        <v>-3.971</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2544</v>
+        <v>4.9238</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3593</v>
+        <v>2.7495</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8952</v>
+        <v>2.1743</v>
       </c>
       <c r="G15" t="n">
-        <v>5.0229</v>
+        <v>5.0272</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8455</v>
+        <v>1.8467</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1773</v>
+        <v>3.1805</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4541</v>
+        <v>4.4384</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4763</v>
+        <v>2.4649</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9778</v>
+        <v>1.9736</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5688</v>
+        <v>0.5887</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4584</v>
+        <v>1.1243</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4003</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0581</v>
+        <v>0.3093</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2422</v>
+        <v>4.2509</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6867</v>
+        <v>2.6009</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5555</v>
+        <v>1.65</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9421</v>
+        <v>1.9363</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6724</v>
+        <v>-1.6743</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6144</v>
+        <v>3.6107</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0001</v>
+        <v>0.9752</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4125</v>
+        <v>-0.4244</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4126</v>
+        <v>1.3997</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9419</v>
+        <v>0.9611</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O16" t="n">
-        <v>2.2018</v>
+        <v>2.211</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2587</v>
+        <v>1.2659</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8207</v>
+        <v>0.7638</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4379</v>
+        <v>0.5021</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5207</v>
+        <v>3.2315</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7836</v>
+        <v>0.987</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7372</v>
+        <v>2.2445</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5272</v>
+        <v>-0.5302</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.1874</v>
+        <v>-3.1907</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6602</v>
+        <v>2.6605</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3201</v>
+        <v>-1.3494</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.2103</v>
+        <v>-2.2278</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7929</v>
+        <v>0.8192</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O17" t="n">
-        <v>1.77</v>
+        <v>1.7821</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.313</v>
+        <v>0.3959</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1452</v>
+        <v>0.3851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4582</v>
+        <v>0.0108</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>D. NEEDHAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5179</v>
+        <v>2.134</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3087</v>
+        <v>0.4284</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2093</v>
+        <v>1.7056</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0737</v>
+        <v>1.2849</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6016</v>
+        <v>-0.6065</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5278</v>
+        <v>1.8914</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1816</v>
+        <v>1.3567</v>
       </c>
       <c r="K18" t="n">
-        <v>0.107</v>
+        <v>0.6722</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.6845</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2554</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7086</v>
+        <v>-1.2788</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4532</v>
+        <v>1.2069</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>3.1868</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2211</v>
+        <v>-0.1116</v>
       </c>
       <c r="T18" t="n">
-        <v>0.127</v>
+        <v>-0.1072</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3481</v>
+        <v>-0.0044</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2249</v>
+        <v>-0.8603</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
-        <v>0.2249</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. NEEDHAM</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8465</v>
+        <v>1.756</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.255</v>
+        <v>0.1784</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1014</v>
+        <v>1.5776</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2841</v>
+        <v>-0.0746</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6163</v>
+        <v>-0.6112</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9004</v>
+        <v>0.5367</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3763</v>
+        <v>0.1672</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6754</v>
+        <v>0.0927</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7009</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0921</v>
+        <v>-0.2417</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2917</v>
+        <v>-0.7039</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1995</v>
+        <v>0.4622</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.1757</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3846</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8166</v>
+        <v>0.0112</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.0033</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8678</v>
+        <v>0.2292</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4141</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6292</v>
+        <v>-0.4392</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6996</v>
+        <v>-2.0933</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0703</v>
+        <v>1.654</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9409</v>
+        <v>1.9277</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1169</v>
+        <v>2.1113</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.176</v>
+        <v>-0.1836</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3672</v>
+        <v>1.3377</v>
       </c>
       <c r="K20" t="n">
-        <v>1.8977</v>
+        <v>1.8821</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5306</v>
+        <v>-0.5443</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5737</v>
+        <v>0.59</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.3183</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3357</v>
+        <v>-0.0166</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.3017</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6432</v>
+        <v>-0.5226</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5067</v>
+        <v>-3.2916</v>
       </c>
       <c r="F21" t="n">
-        <v>2.8636</v>
+        <v>2.769</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1909</v>
+        <v>-2.1915</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4343</v>
+        <v>-0.4337</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7566</v>
+        <v>-1.7578</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8474</v>
+        <v>-2.8685</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6485</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6565</v>
+        <v>0.677</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4011</v>
+        <v>-0.2903</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6593</v>
+        <v>-0.4231</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2583</v>
+        <v>0.1328</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6582</v>
+        <v>-1.6051</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8979</v>
+        <v>-3.9459</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2397</v>
+        <v>2.3407</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3657</v>
+        <v>-0.3761</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0432</v>
+        <v>-0.0513</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3225</v>
+        <v>-0.3248</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6441</v>
+        <v>-0.6794</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4462</v>
+        <v>0.4234</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2784</v>
+        <v>0.3033</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1337</v>
+        <v>-0.0697</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0121</v>
+        <v>-0.0097</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1216</v>
+        <v>-0.06</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4592</v>
+        <v>-2.6648</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3452</v>
+        <v>-3.032</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.114</v>
+        <v>0.3671</v>
       </c>
       <c r="G23" t="n">
-        <v>1.3515</v>
+        <v>1.3481</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4213</v>
+        <v>0.4249</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9302</v>
+        <v>0.9233</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3608</v>
+        <v>1.333</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0434</v>
+        <v>2.0339</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0094</v>
+        <v>0.0151</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O23" t="n">
-        <v>1.6127</v>
+        <v>1.6242</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R23" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2643</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0575</v>
+        <v>0.4153</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3218</v>
+        <v>0.1165</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1376</v>
+        <v>-4.051</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.0651</v>
+        <v>-5.5123</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9275</v>
+        <v>1.4613</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5592</v>
+        <v>-3.5701</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.1989</v>
+        <v>-4.2044</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6397</v>
+        <v>0.6343</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.4985</v>
+        <v>-4.534</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.7413</v>
+        <v>-3.7586</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7572</v>
+        <v>-0.7754</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9392</v>
+        <v>0.9639</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O24" t="n">
-        <v>1.3968</v>
+        <v>1.4097</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1662</v>
+        <v>-0.0743</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4325</v>
+        <v>0.1599</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7337</v>
+        <v>-0.2342</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.854300000000001</v>
+        <v>7.013499999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.6312</v>
+        <v>-10.9309</v>
       </c>
       <c r="F25" t="n">
-        <v>14.4857</v>
+        <v>17.9441</v>
       </c>
       <c r="G25" t="n">
-        <v>4.8248</v>
+        <v>4.781699999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.3704</v>
+        <v>-6.3892</v>
       </c>
       <c r="I25" t="n">
-        <v>11.1949</v>
+        <v>11.1712</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4299999999999997</v>
+        <v>0.1768999999999998</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6443000000000003</v>
+        <v>0.5099000000000014</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2142999999999999</v>
+        <v>-0.3329000000000002</v>
       </c>
       <c r="M25" t="n">
-        <v>4.3945</v>
+        <v>4.6047</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.0147</v>
+        <v>-6.8993</v>
       </c>
       <c r="O25" t="n">
-        <v>11.4091</v>
+        <v>11.504</v>
       </c>
       <c r="P25" t="n">
-        <v>5.6708</v>
+        <v>5.6907</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R25" t="n">
-        <v>22.6835</v>
+        <v>22.7631</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6955999999999998</v>
+        <v>2.4616</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9659</v>
+        <v>1.9937</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.6615</v>
+        <v>0.4679</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.9455</v>
+        <v>-5.920599999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>3.984999999999999</v>
+        <v>3.9709</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.9306</v>
+        <v>-9.891599999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104599_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104599_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-3.971</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104599_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.891599999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
